--- a/data/trans_camb/IP13-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP13-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,07</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,71</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-1,69</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,76</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,07</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,71</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,48</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>5,05</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 6,82</t>
+          <t>-5,41; 7,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 4,38</t>
+          <t>-9,06; 2,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 12,97</t>
+          <t>-2,9; 15,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 7,6</t>
+          <t>-4,17; 6,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 2,25</t>
+          <t>-6,31; 4,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 14,94</t>
+          <t>-1,73; 14,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 5,44</t>
+          <t>-3,23; 5,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 1,53</t>
+          <t>-6,23; 1,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 10,55</t>
+          <t>-0,2; 11,65</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15,39%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-53,18%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>74,56%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>27,25%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-32,52%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>72,31%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,39%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-53,18%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>83,29%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-62,89; 278,08</t>
+          <t>-60,28; 222,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 233,13</t>
+          <t>-92,97; 107,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,4; 484,97</t>
+          <t>-36,85; 351,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,62; 181,07</t>
+          <t>-56,2; 258,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-89,25; 92,92</t>
+          <t>-88,1; 221,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 395,95</t>
+          <t>-36,14; 551,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,14; 133,92</t>
+          <t>-42,81; 137,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,92; 62,3</t>
+          <t>-79,86; 53,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 251,98</t>
+          <t>-8,72; 271,13</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,34</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,38</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,25</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,31</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,02</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,61</t>
+          <t>-0,17; 4,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,37</t>
+          <t>-1,75; 2,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,26</t>
+          <t>-1,05; 3,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 5,07</t>
+          <t>-2,05; 2,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,32</t>
+          <t>-2,54; 2,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,91</t>
+          <t>-2,31; 2,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,03</t>
+          <t>-0,35; 3,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,79</t>
+          <t>-1,38; 1,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,21</t>
+          <t>-0,89; 2,36</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>51,94%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27,73%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>6,11%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,26%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>51,94%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,84; 67,83</t>
+          <t>-3,67; 142,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,03; 60,11</t>
+          <t>-32,78; 84,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 59,75</t>
+          <t>-19,05; 112,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 139,01</t>
+          <t>-34,3; 67,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,97; 70,42</t>
+          <t>-40,04; 64,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 110,27</t>
+          <t>-37,17; 64,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 74,2</t>
+          <t>-6,45; 81,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 44,0</t>
+          <t>-25,08; 47,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 55,59</t>
+          <t>-17,45; 60,39</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,82</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,33</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>2,34</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>3,72</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,92</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,23</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,82</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>2,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 5,97</t>
+          <t>-5,95; 1,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 7,46</t>
+          <t>-5,58; 1,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 8,44</t>
+          <t>-2,81; 6,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 1,21</t>
+          <t>-0,66; 6,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 1,45</t>
+          <t>0,62; 7,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 5,41</t>
+          <t>0,4; 8,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,38</t>
+          <t>-2,27; 2,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,36</t>
+          <t>-1,58; 3,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 5,57</t>
+          <t>0,24; 6,15</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-41,13%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-33,69%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24,59%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>84,66%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>134,59%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>142,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-41,13%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-33,69%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>148,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>69,06%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,67; 374,35</t>
+          <t>-78,69; 59,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 431,77</t>
+          <t>-71,64; 57,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 521,76</t>
+          <t>-38,48; 181,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-82,03; 49,13</t>
+          <t>-31,14; 386,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,75; 52,35</t>
+          <t>10,85; 541,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,53; 160,76</t>
+          <t>1,63; 544,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-47,93; 78,98</t>
+          <t>-44,01; 99,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 114,33</t>
+          <t>-33,84; 110,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 190,09</t>
+          <t>0,66; 204,83</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,59</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,51</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,97</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,8</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,78</t>
+          <t>-0,72; 3,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,64</t>
+          <t>-2,56; 1,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,17</t>
+          <t>-0,46; 3,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,07</t>
+          <t>-0,95; 3,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,31</t>
+          <t>-1,0; 2,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,71</t>
+          <t>-0,65; 3,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,38</t>
+          <t>-0,25; 2,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,31</t>
+          <t>-1,23; 1,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,7</t>
+          <t>0,21; 2,87</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>22,86%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-11,77%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>30,21%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>21,79%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>17,84%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>26,28%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>22,86%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-11,77%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 78,53</t>
+          <t>-12,34; 70,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 74,82</t>
+          <t>-41,03; 29,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 89,14</t>
+          <t>-7,98; 85,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 74,45</t>
+          <t>-17,93; 85,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,0; 32,57</t>
+          <t>-18,98; 69,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 92,02</t>
+          <t>-13,45; 95,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 58,0</t>
+          <t>-4,61; 59,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 32,24</t>
+          <t>-22,47; 35,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 65,39</t>
+          <t>3,28; 68,6</t>
         </is>
       </c>
     </row>
